--- a/docs/vhs/fixtures/sales.xlsx
+++ b/docs/vhs/fixtures/sales.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Category</t>
   </si>
@@ -25,10 +25,25 @@
     <t>Shoes</t>
   </si>
   <si>
+    <t>1200</t>
+  </si>
+  <si>
     <t>Shirts</t>
   </si>
   <si>
+    <t>850</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
     <t>Hats</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>400</t>
   </si>
 </sst>
 </file>
@@ -347,40 +362,40 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>1200</v>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>850</v>
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>300</v>
+      <c r="B4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>150</v>
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>400</v>
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
